--- a/data/exploration/training_data/description_training_sample_42.xlsx
+++ b/data/exploration/training_data/description_training_sample_42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PyhcarmProjects\youtube_data\data\exploration\training_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353A3A4B-7140-41B2-B396-0221ACCC7791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DAEDE92-74C2-492B-AA64-7A33E61C2CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4113,14 +4113,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -4153,13 +4158,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F7495F-BBA1-4ECC-982C-E9796D72D607}" name="Table1" displayName="Table1" ref="A1:E201" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69F7495F-BBA1-4ECC-982C-E9796D72D607}" name="Table1" displayName="Table1" ref="A1:E201" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:E201" xr:uid="{69F7495F-BBA1-4ECC-982C-E9796D72D607}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{08A672ED-44AA-4E6F-8443-5D6935AC5F73}" name="video_id"/>
     <tableColumn id="2" xr3:uid="{58F4D10D-8157-4941-B8DC-0065434E2BFF}" name="title"/>
     <tableColumn id="3" xr3:uid="{120FEFE1-66C7-4EA2-B466-73B5F396D799}" name="description"/>
-    <tableColumn id="4" xr3:uid="{DE131A3D-AC9C-464C-82C9-6BDE8C7D5A77}" name="politics_title"/>
+    <tableColumn id="4" xr3:uid="{DE131A3D-AC9C-464C-82C9-6BDE8C7D5A77}" name="politics_title" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{8C0C5B6A-A7BF-46A9-8DEA-40044E7927F8}" name="politics_title_desc"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4471,7 +4476,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>401</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -4488,7 +4493,7 @@
       <c r="C2" t="s">
         <v>404</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4502,7 +4507,7 @@
       <c r="C3" t="s">
         <v>405</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>-1</v>
       </c>
       <c r="E3">
@@ -4519,7 +4524,7 @@
       <c r="C4" t="s">
         <v>406</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4533,7 +4538,7 @@
       <c r="C5" t="s">
         <v>407</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4547,7 +4552,7 @@
       <c r="C6" t="s">
         <v>408</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4561,7 +4566,7 @@
       <c r="C7" t="s">
         <v>409</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>-1</v>
       </c>
       <c r="E7">
@@ -4578,7 +4583,7 @@
       <c r="C8" t="s">
         <v>410</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4592,7 +4597,7 @@
       <c r="C9" t="s">
         <v>411</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4606,7 +4611,7 @@
       <c r="C10" t="s">
         <v>412</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4620,7 +4625,7 @@
       <c r="C11" t="s">
         <v>413</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4634,7 +4639,7 @@
       <c r="C12" t="s">
         <v>414</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4648,7 +4653,7 @@
       <c r="C13" t="s">
         <v>415</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4662,7 +4667,7 @@
       <c r="C14" t="s">
         <v>416</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4676,7 +4681,7 @@
       <c r="C15" t="s">
         <v>417</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>-1</v>
       </c>
       <c r="E15">
@@ -4693,7 +4698,7 @@
       <c r="C16" t="s">
         <v>418</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4707,7 +4712,7 @@
       <c r="C17" t="s">
         <v>419</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4721,7 +4726,7 @@
       <c r="C18" t="s">
         <v>420</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>-1</v>
       </c>
       <c r="E18">
@@ -4738,7 +4743,7 @@
       <c r="C19" t="s">
         <v>421</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4752,7 +4757,7 @@
       <c r="C20" t="s">
         <v>422</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4766,7 +4771,7 @@
       <c r="C21" t="s">
         <v>423</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4780,7 +4785,7 @@
       <c r="C22" t="s">
         <v>424</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4794,7 +4799,7 @@
       <c r="C23" t="s">
         <v>425</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4808,7 +4813,7 @@
       <c r="C24" t="s">
         <v>426</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>-1</v>
       </c>
       <c r="E24">
@@ -4825,7 +4830,7 @@
       <c r="C25" t="s">
         <v>427</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4839,7 +4844,7 @@
       <c r="C26" t="s">
         <v>428</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>-1</v>
       </c>
       <c r="E26">
@@ -4856,7 +4861,7 @@
       <c r="C27" t="s">
         <v>429</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>-1</v>
       </c>
       <c r="E27">
@@ -4870,7 +4875,7 @@
       <c r="B28" t="s">
         <v>56</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>-1</v>
       </c>
       <c r="E28">
@@ -4887,7 +4892,7 @@
       <c r="C29" t="s">
         <v>430</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4901,7 +4906,7 @@
       <c r="C30" t="s">
         <v>431</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4915,7 +4920,7 @@
       <c r="C31" t="s">
         <v>432</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4929,7 +4934,7 @@
       <c r="C32" t="s">
         <v>433</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4943,7 +4948,7 @@
       <c r="C33" t="s">
         <v>434</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4957,7 +4962,7 @@
       <c r="C34" t="s">
         <v>435</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4971,7 +4976,7 @@
       <c r="C35" t="s">
         <v>436</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4985,7 +4990,7 @@
       <c r="C36" t="s">
         <v>437</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4999,7 +5004,7 @@
       <c r="C37" t="s">
         <v>438</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5013,7 +5018,7 @@
       <c r="C38" t="s">
         <v>439</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5027,7 +5032,7 @@
       <c r="C39" t="s">
         <v>440</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5041,7 +5046,7 @@
       <c r="C40" t="s">
         <v>441</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5055,7 +5060,7 @@
       <c r="C41" t="s">
         <v>442</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="2">
         <v>-1</v>
       </c>
       <c r="E41">
@@ -5072,7 +5077,7 @@
       <c r="C42" t="s">
         <v>443</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5086,7 +5091,7 @@
       <c r="C43" t="s">
         <v>444</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5100,7 +5105,7 @@
       <c r="C44" t="s">
         <v>445</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5111,7 +5116,7 @@
       <c r="B45" t="s">
         <v>90</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5125,7 +5130,7 @@
       <c r="C46" t="s">
         <v>446</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5139,7 +5144,7 @@
       <c r="C47" t="s">
         <v>447</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5153,7 +5158,7 @@
       <c r="C48" t="s">
         <v>448</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5167,7 +5172,7 @@
       <c r="C49" t="s">
         <v>449</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5181,7 +5186,7 @@
       <c r="C50" t="s">
         <v>450</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5195,7 +5200,7 @@
       <c r="C51" t="s">
         <v>451</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5209,7 +5214,7 @@
       <c r="C52" t="s">
         <v>452</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="2">
         <v>-1</v>
       </c>
       <c r="E52">
@@ -5226,7 +5231,7 @@
       <c r="C53" t="s">
         <v>453</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5240,7 +5245,7 @@
       <c r="C54" t="s">
         <v>454</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5254,7 +5259,7 @@
       <c r="C55" t="s">
         <v>455</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5268,7 +5273,7 @@
       <c r="C56" t="s">
         <v>456</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="2">
         <v>-1</v>
       </c>
       <c r="E56">
@@ -5285,7 +5290,7 @@
       <c r="C57" t="s">
         <v>457</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5299,7 +5304,7 @@
       <c r="C58" t="s">
         <v>458</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="2">
         <v>-1</v>
       </c>
       <c r="E58">
@@ -5316,7 +5321,7 @@
       <c r="C59" t="s">
         <v>459</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="2">
         <v>-1</v>
       </c>
       <c r="E59">
@@ -5333,7 +5338,7 @@
       <c r="C60" t="s">
         <v>460</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5347,7 +5352,7 @@
       <c r="C61" t="s">
         <v>461</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="2">
         <v>-1</v>
       </c>
       <c r="E61">
@@ -5364,7 +5369,7 @@
       <c r="C62" t="s">
         <v>462</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5375,7 +5380,7 @@
       <c r="B63" t="s">
         <v>126</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="2">
         <v>-1</v>
       </c>
       <c r="E63">
@@ -5389,7 +5394,7 @@
       <c r="B64" t="s">
         <v>128</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5400,7 +5405,7 @@
       <c r="B65" t="s">
         <v>130</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5414,7 +5419,7 @@
       <c r="C66" t="s">
         <v>463</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="2">
         <v>-1</v>
       </c>
       <c r="E66">
@@ -5431,7 +5436,7 @@
       <c r="C67" t="s">
         <v>464</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5445,7 +5450,7 @@
       <c r="C68" t="s">
         <v>465</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5459,7 +5464,7 @@
       <c r="C69" t="s">
         <v>466</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5473,7 +5478,7 @@
       <c r="C70" t="s">
         <v>467</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5487,7 +5492,7 @@
       <c r="C71" t="s">
         <v>468</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5501,7 +5506,7 @@
       <c r="C72" t="s">
         <v>469</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5515,7 +5520,7 @@
       <c r="C73" t="s">
         <v>470</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5529,7 +5534,7 @@
       <c r="C74" t="s">
         <v>471</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5543,7 +5548,7 @@
       <c r="C75" t="s">
         <v>472</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5557,7 +5562,7 @@
       <c r="C76" t="s">
         <v>473</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5571,7 +5576,7 @@
       <c r="C77" t="s">
         <v>474</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5585,7 +5590,7 @@
       <c r="C78" t="s">
         <v>475</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5599,7 +5604,7 @@
       <c r="C79" t="s">
         <v>476</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5613,7 +5618,7 @@
       <c r="C80" t="s">
         <v>477</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="2">
         <v>-1</v>
       </c>
       <c r="E80">
@@ -5630,7 +5635,7 @@
       <c r="C81" t="s">
         <v>478</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5644,7 +5649,7 @@
       <c r="C82" t="s">
         <v>479</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="2">
         <v>-1</v>
       </c>
       <c r="E82">
@@ -5661,7 +5666,7 @@
       <c r="C83" t="s">
         <v>480</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5675,7 +5680,7 @@
       <c r="C84" t="s">
         <v>481</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="2">
         <v>-1</v>
       </c>
       <c r="E84">
@@ -5692,7 +5697,7 @@
       <c r="C85" t="s">
         <v>482</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5703,7 +5708,7 @@
       <c r="B86" t="s">
         <v>172</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5717,7 +5722,7 @@
       <c r="C87" t="s">
         <v>483</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="2">
         <v>-1</v>
       </c>
       <c r="E87">
@@ -5734,7 +5739,7 @@
       <c r="C88" t="s">
         <v>484</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5748,7 +5753,7 @@
       <c r="C89" t="s">
         <v>485</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="2">
         <v>-1</v>
       </c>
       <c r="E89">
@@ -5765,7 +5770,7 @@
       <c r="C90" t="s">
         <v>486</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="2">
         <v>-1</v>
       </c>
       <c r="E90">
@@ -5782,7 +5787,7 @@
       <c r="C91" t="s">
         <v>487</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="2">
         <v>-1</v>
       </c>
       <c r="E91">
@@ -5799,7 +5804,7 @@
       <c r="C92" t="s">
         <v>488</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5813,7 +5818,7 @@
       <c r="C93" t="s">
         <v>489</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="2">
         <v>-1</v>
       </c>
       <c r="E93">
@@ -5830,7 +5835,7 @@
       <c r="C94" t="s">
         <v>490</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5844,7 +5849,7 @@
       <c r="C95" t="s">
         <v>491</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="2">
         <v>-1</v>
       </c>
       <c r="E95">
@@ -5861,7 +5866,7 @@
       <c r="C96" t="s">
         <v>492</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5875,7 +5880,7 @@
       <c r="C97" t="s">
         <v>493</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5889,7 +5894,7 @@
       <c r="C98" t="s">
         <v>494</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="2">
         <v>-1</v>
       </c>
       <c r="E98">
@@ -5906,7 +5911,7 @@
       <c r="C99" t="s">
         <v>495</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5920,7 +5925,7 @@
       <c r="C100" t="s">
         <v>496</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5934,7 +5939,7 @@
       <c r="C101" t="s">
         <v>497</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="2">
         <v>-1</v>
       </c>
       <c r="E101">
@@ -5951,7 +5956,7 @@
       <c r="C102" t="s">
         <v>498</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="2">
         <v>-1</v>
       </c>
       <c r="E102">
@@ -5968,7 +5973,7 @@
       <c r="C103" t="s">
         <v>499</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="2">
         <v>-1</v>
       </c>
       <c r="E103">
@@ -5985,7 +5990,7 @@
       <c r="C104" t="s">
         <v>500</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5999,7 +6004,7 @@
       <c r="C105" t="s">
         <v>501</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6013,7 +6018,7 @@
       <c r="C106" t="s">
         <v>502</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6027,7 +6032,7 @@
       <c r="C107" t="s">
         <v>503</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="2">
         <v>-1</v>
       </c>
       <c r="E107">
@@ -6044,7 +6049,7 @@
       <c r="C108" t="s">
         <v>504</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="2">
         <v>-1</v>
       </c>
       <c r="E108">
@@ -6061,7 +6066,7 @@
       <c r="C109" t="s">
         <v>505</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6075,7 +6080,7 @@
       <c r="C110" t="s">
         <v>506</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="2">
         <v>-1</v>
       </c>
       <c r="E110">
@@ -6092,7 +6097,7 @@
       <c r="C111" t="s">
         <v>507</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6103,7 +6108,7 @@
       <c r="B112" t="s">
         <v>222</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6117,7 +6122,7 @@
       <c r="C113" t="s">
         <v>508</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6131,7 +6136,7 @@
       <c r="C114" t="s">
         <v>509</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6145,7 +6150,7 @@
       <c r="C115" t="s">
         <v>510</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6159,7 +6164,7 @@
       <c r="C116" t="s">
         <v>511</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6173,7 +6178,7 @@
       <c r="C117" t="s">
         <v>512</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="2">
         <v>-1</v>
       </c>
       <c r="E117">
@@ -6190,7 +6195,7 @@
       <c r="C118" t="s">
         <v>513</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6204,7 +6209,7 @@
       <c r="C119" t="s">
         <v>514</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="2">
         <v>-1</v>
       </c>
       <c r="E119">
@@ -6221,7 +6226,7 @@
       <c r="C120" t="s">
         <v>515</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6235,7 +6240,7 @@
       <c r="C121" t="s">
         <v>516</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="2">
         <v>-1</v>
       </c>
       <c r="E121">
@@ -6252,7 +6257,7 @@
       <c r="C122" t="s">
         <v>517</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6266,7 +6271,7 @@
       <c r="C123" t="s">
         <v>518</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6280,7 +6285,7 @@
       <c r="C124" t="s">
         <v>519</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6294,7 +6299,7 @@
       <c r="C125" t="s">
         <v>520</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6308,7 +6313,7 @@
       <c r="C126" t="s">
         <v>521</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6322,7 +6327,7 @@
       <c r="C127" t="s">
         <v>522</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="2">
         <v>-1</v>
       </c>
       <c r="E127">
@@ -6339,7 +6344,7 @@
       <c r="C128" t="s">
         <v>523</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6353,7 +6358,7 @@
       <c r="C129" t="s">
         <v>524</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6367,7 +6372,7 @@
       <c r="C130" t="s">
         <v>525</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6381,7 +6386,7 @@
       <c r="C131" t="s">
         <v>526</v>
       </c>
-      <c r="D131">
+      <c r="D131" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6395,7 +6400,7 @@
       <c r="C132" t="s">
         <v>527</v>
       </c>
-      <c r="D132">
+      <c r="D132" s="2">
         <v>-1</v>
       </c>
       <c r="E132">
@@ -6412,7 +6417,7 @@
       <c r="C133" t="s">
         <v>528</v>
       </c>
-      <c r="D133">
+      <c r="D133" s="2">
         <v>-1</v>
       </c>
       <c r="E133">
@@ -6429,7 +6434,7 @@
       <c r="C134" t="s">
         <v>529</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6440,7 +6445,7 @@
       <c r="B135" t="s">
         <v>268</v>
       </c>
-      <c r="D135">
+      <c r="D135" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6454,7 +6459,7 @@
       <c r="C136" t="s">
         <v>530</v>
       </c>
-      <c r="D136">
+      <c r="D136" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6468,7 +6473,7 @@
       <c r="C137" t="s">
         <v>531</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6482,7 +6487,7 @@
       <c r="C138" t="s">
         <v>532</v>
       </c>
-      <c r="D138">
+      <c r="D138" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6496,7 +6501,7 @@
       <c r="C139" t="s">
         <v>533</v>
       </c>
-      <c r="D139">
+      <c r="D139" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6510,7 +6515,7 @@
       <c r="C140" t="s">
         <v>534</v>
       </c>
-      <c r="D140">
+      <c r="D140" s="2">
         <v>-1</v>
       </c>
       <c r="E140">
@@ -6527,7 +6532,7 @@
       <c r="C141" t="s">
         <v>535</v>
       </c>
-      <c r="D141">
+      <c r="D141" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6538,7 +6543,7 @@
       <c r="B142" t="s">
         <v>282</v>
       </c>
-      <c r="D142">
+      <c r="D142" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6552,7 +6557,7 @@
       <c r="C143" t="s">
         <v>536</v>
       </c>
-      <c r="D143">
+      <c r="D143" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6566,7 +6571,7 @@
       <c r="C144" t="s">
         <v>537</v>
       </c>
-      <c r="D144">
+      <c r="D144" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6580,7 +6585,7 @@
       <c r="C145" t="s">
         <v>538</v>
       </c>
-      <c r="D145">
+      <c r="D145" s="2">
         <v>-1</v>
       </c>
       <c r="E145">
@@ -6597,7 +6602,7 @@
       <c r="C146" t="s">
         <v>539</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6611,7 +6616,7 @@
       <c r="C147" t="s">
         <v>540</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6625,7 +6630,7 @@
       <c r="C148" t="s">
         <v>541</v>
       </c>
-      <c r="D148">
+      <c r="D148" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6639,7 +6644,7 @@
       <c r="C149" t="s">
         <v>542</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="2">
         <v>-1</v>
       </c>
       <c r="E149">
@@ -6653,7 +6658,7 @@
       <c r="B150" t="s">
         <v>298</v>
       </c>
-      <c r="D150">
+      <c r="D150" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6667,7 +6672,7 @@
       <c r="C151" t="s">
         <v>543</v>
       </c>
-      <c r="D151">
+      <c r="D151" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6681,7 +6686,7 @@
       <c r="C152" t="s">
         <v>544</v>
       </c>
-      <c r="D152">
+      <c r="D152" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6695,7 +6700,7 @@
       <c r="C153" t="s">
         <v>545</v>
       </c>
-      <c r="D153">
+      <c r="D153" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6709,7 +6714,7 @@
       <c r="C154" t="s">
         <v>546</v>
       </c>
-      <c r="D154">
+      <c r="D154" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6723,7 +6728,7 @@
       <c r="C155" t="s">
         <v>547</v>
       </c>
-      <c r="D155">
+      <c r="D155" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6737,7 +6742,7 @@
       <c r="C156" t="s">
         <v>548</v>
       </c>
-      <c r="D156">
+      <c r="D156" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6751,7 +6756,7 @@
       <c r="C157" t="s">
         <v>549</v>
       </c>
-      <c r="D157">
+      <c r="D157" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6765,7 +6770,7 @@
       <c r="C158" t="s">
         <v>550</v>
       </c>
-      <c r="D158">
+      <c r="D158" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6779,7 +6784,7 @@
       <c r="C159" t="s">
         <v>551</v>
       </c>
-      <c r="D159">
+      <c r="D159" s="2">
         <v>-1</v>
       </c>
       <c r="E159">
@@ -6796,7 +6801,7 @@
       <c r="C160" t="s">
         <v>552</v>
       </c>
-      <c r="D160">
+      <c r="D160" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6810,7 +6815,7 @@
       <c r="C161" t="s">
         <v>553</v>
       </c>
-      <c r="D161">
+      <c r="D161" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6824,7 +6829,7 @@
       <c r="C162" t="s">
         <v>554</v>
       </c>
-      <c r="D162">
+      <c r="D162" s="2">
         <v>-1</v>
       </c>
       <c r="E162">
@@ -6841,7 +6846,7 @@
       <c r="C163" t="s">
         <v>555</v>
       </c>
-      <c r="D163">
+      <c r="D163" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6855,7 +6860,7 @@
       <c r="C164" t="s">
         <v>556</v>
       </c>
-      <c r="D164">
+      <c r="D164" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6869,7 +6874,7 @@
       <c r="C165" t="s">
         <v>557</v>
       </c>
-      <c r="D165">
+      <c r="D165" s="2">
         <v>-1</v>
       </c>
       <c r="E165">
@@ -6886,7 +6891,7 @@
       <c r="C166" t="s">
         <v>558</v>
       </c>
-      <c r="D166">
+      <c r="D166" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6897,7 +6902,7 @@
       <c r="B167" t="s">
         <v>332</v>
       </c>
-      <c r="D167">
+      <c r="D167" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6911,7 +6916,7 @@
       <c r="C168" t="s">
         <v>559</v>
       </c>
-      <c r="D168">
+      <c r="D168" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6922,7 +6927,7 @@
       <c r="B169" t="s">
         <v>336</v>
       </c>
-      <c r="D169">
+      <c r="D169" s="2">
         <v>-1</v>
       </c>
       <c r="E169">
@@ -6939,7 +6944,7 @@
       <c r="C170" t="s">
         <v>560</v>
       </c>
-      <c r="D170">
+      <c r="D170" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6953,7 +6958,7 @@
       <c r="C171" t="s">
         <v>561</v>
       </c>
-      <c r="D171">
+      <c r="D171" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6967,7 +6972,7 @@
       <c r="C172" t="s">
         <v>562</v>
       </c>
-      <c r="D172">
+      <c r="D172" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6981,7 +6986,7 @@
       <c r="C173" t="s">
         <v>563</v>
       </c>
-      <c r="D173">
+      <c r="D173" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6995,9 +7000,10 @@
       <c r="C174" t="s">
         <v>564</v>
       </c>
-      <c r="D174">
+      <c r="D174" s="2">
         <v>0</v>
       </c>
+      <c r="E174" s="2"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
@@ -7009,9 +7015,10 @@
       <c r="C175" t="s">
         <v>565</v>
       </c>
-      <c r="D175">
-        <v>1</v>
-      </c>
+      <c r="D175" s="2">
+        <v>1</v>
+      </c>
+      <c r="E175" s="2"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
@@ -7023,9 +7030,10 @@
       <c r="C176" t="s">
         <v>566</v>
       </c>
-      <c r="D176">
-        <v>1</v>
-      </c>
+      <c r="D176" s="2">
+        <v>1</v>
+      </c>
+      <c r="E176" s="2"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
@@ -7037,9 +7045,10 @@
       <c r="C177" t="s">
         <v>567</v>
       </c>
-      <c r="D177">
-        <v>1</v>
-      </c>
+      <c r="D177" s="2">
+        <v>1</v>
+      </c>
+      <c r="E177" s="2"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
@@ -7051,9 +7060,10 @@
       <c r="C178" t="s">
         <v>568</v>
       </c>
-      <c r="D178">
-        <v>1</v>
-      </c>
+      <c r="D178" s="2">
+        <v>1</v>
+      </c>
+      <c r="E178" s="2"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
@@ -7065,9 +7075,10 @@
       <c r="C179" t="s">
         <v>569</v>
       </c>
-      <c r="D179">
-        <v>1</v>
-      </c>
+      <c r="D179" s="2">
+        <v>1</v>
+      </c>
+      <c r="E179" s="2"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
@@ -7079,9 +7090,10 @@
       <c r="C180" t="s">
         <v>570</v>
       </c>
-      <c r="D180">
+      <c r="D180" s="2">
         <v>0</v>
       </c>
+      <c r="E180" s="2"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
@@ -7093,9 +7105,10 @@
       <c r="C181" t="s">
         <v>571</v>
       </c>
-      <c r="D181">
-        <v>1</v>
-      </c>
+      <c r="D181" s="2">
+        <v>1</v>
+      </c>
+      <c r="E181" s="2"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
@@ -7107,9 +7120,10 @@
       <c r="C182" t="s">
         <v>572</v>
       </c>
-      <c r="D182">
-        <v>1</v>
-      </c>
+      <c r="D182" s="2">
+        <v>1</v>
+      </c>
+      <c r="E182" s="2"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
@@ -7121,9 +7135,10 @@
       <c r="C183" t="s">
         <v>573</v>
       </c>
-      <c r="D183">
-        <v>1</v>
-      </c>
+      <c r="D183" s="2">
+        <v>1</v>
+      </c>
+      <c r="E183" s="2"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
@@ -7135,9 +7150,10 @@
       <c r="C184" t="s">
         <v>574</v>
       </c>
-      <c r="D184">
-        <v>1</v>
-      </c>
+      <c r="D184" s="2">
+        <v>1</v>
+      </c>
+      <c r="E184" s="2"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
@@ -7149,9 +7165,10 @@
       <c r="C185" t="s">
         <v>575</v>
       </c>
-      <c r="D185">
+      <c r="D185" s="2">
         <v>0</v>
       </c>
+      <c r="E185" s="2"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
@@ -7163,9 +7180,10 @@
       <c r="C186" t="s">
         <v>576</v>
       </c>
-      <c r="D186">
+      <c r="D186" s="2">
         <v>0</v>
       </c>
+      <c r="E186" s="2"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
@@ -7177,10 +7195,10 @@
       <c r="C187" t="s">
         <v>577</v>
       </c>
-      <c r="D187">
+      <c r="D187" s="2">
         <v>-1</v>
       </c>
-      <c r="E187">
+      <c r="E187" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7194,10 +7212,10 @@
       <c r="C188" t="s">
         <v>578</v>
       </c>
-      <c r="D188">
+      <c r="D188" s="2">
         <v>-1</v>
       </c>
-      <c r="E188">
+      <c r="E188" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -7211,10 +7229,10 @@
       <c r="C189" t="s">
         <v>579</v>
       </c>
-      <c r="D189">
+      <c r="D189" s="2">
         <v>-1</v>
       </c>
-      <c r="E189">
+      <c r="E189" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7228,9 +7246,10 @@
       <c r="C190" t="s">
         <v>580</v>
       </c>
-      <c r="D190">
+      <c r="D190" s="2">
         <v>0</v>
       </c>
+      <c r="E190" s="2"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
@@ -7242,9 +7261,10 @@
       <c r="C191" t="s">
         <v>581</v>
       </c>
-      <c r="D191">
-        <v>1</v>
-      </c>
+      <c r="D191" s="2">
+        <v>1</v>
+      </c>
+      <c r="E191" s="2"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
@@ -7256,9 +7276,10 @@
       <c r="C192" t="s">
         <v>582</v>
       </c>
-      <c r="D192">
-        <v>1</v>
-      </c>
+      <c r="D192" s="2">
+        <v>1</v>
+      </c>
+      <c r="E192" s="2"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
@@ -7270,10 +7291,10 @@
       <c r="C193" t="s">
         <v>583</v>
       </c>
-      <c r="D193">
+      <c r="D193" s="2">
         <v>-1</v>
       </c>
-      <c r="E193">
+      <c r="E193" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -7287,10 +7308,10 @@
       <c r="C194" t="s">
         <v>584</v>
       </c>
-      <c r="D194">
+      <c r="D194" s="2">
         <v>-1</v>
       </c>
-      <c r="E194">
+      <c r="E194" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7304,9 +7325,10 @@
       <c r="C195" t="s">
         <v>585</v>
       </c>
-      <c r="D195">
-        <v>1</v>
-      </c>
+      <c r="D195" s="2">
+        <v>1</v>
+      </c>
+      <c r="E195" s="2"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
@@ -7318,9 +7340,10 @@
       <c r="C196" t="s">
         <v>586</v>
       </c>
-      <c r="D196">
-        <v>1</v>
-      </c>
+      <c r="D196" s="2">
+        <v>1</v>
+      </c>
+      <c r="E196" s="2"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
@@ -7332,9 +7355,10 @@
       <c r="C197" t="s">
         <v>587</v>
       </c>
-      <c r="D197">
-        <v>1</v>
-      </c>
+      <c r="D197" s="2">
+        <v>1</v>
+      </c>
+      <c r="E197" s="2"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
@@ -7346,10 +7370,10 @@
       <c r="C198" t="s">
         <v>588</v>
       </c>
-      <c r="D198">
+      <c r="D198" s="2">
         <v>-1</v>
       </c>
-      <c r="E198">
+      <c r="E198" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7363,9 +7387,10 @@
       <c r="C199" t="s">
         <v>589</v>
       </c>
-      <c r="D199">
-        <v>1</v>
-      </c>
+      <c r="D199" s="2">
+        <v>1</v>
+      </c>
+      <c r="E199" s="2"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
@@ -7377,9 +7402,10 @@
       <c r="C200" t="s">
         <v>590</v>
       </c>
-      <c r="D200">
-        <v>1</v>
-      </c>
+      <c r="D200" s="2">
+        <v>1</v>
+      </c>
+      <c r="E200" s="2"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
@@ -7391,10 +7417,10 @@
       <c r="C201" t="s">
         <v>591</v>
       </c>
-      <c r="D201">
+      <c r="D201" s="2">
         <v>-1</v>
       </c>
-      <c r="E201">
+      <c r="E201" s="2">
         <v>-1</v>
       </c>
     </row>

--- a/data/exploration/training_data/description_training_sample_42.xlsx
+++ b/data/exploration/training_data/description_training_sample_42.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PyhcarmProjects\youtube_data\data\exploration\training_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DAEDE92-74C2-492B-AA64-7A33E61C2CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21656A2-77B2-472E-A619-3BA0AAE4B183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5479,7 +5479,7 @@
         <v>467</v>
       </c>
       <c r="D70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -5681,10 +5681,7 @@
         <v>481</v>
       </c>
       <c r="D84" s="2">
-        <v>-1</v>
-      </c>
-      <c r="E84">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -6033,10 +6030,7 @@
         <v>503</v>
       </c>
       <c r="D107" s="2">
-        <v>-1</v>
-      </c>
-      <c r="E107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -6050,10 +6044,7 @@
         <v>504</v>
       </c>
       <c r="D108" s="2">
-        <v>-1</v>
-      </c>
-      <c r="E108">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -6418,10 +6409,10 @@
         <v>528</v>
       </c>
       <c r="D133" s="2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E133">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -6533,7 +6524,7 @@
         <v>535</v>
       </c>
       <c r="D141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -6928,10 +6919,7 @@
         <v>336</v>
       </c>
       <c r="D169" s="2">
-        <v>-1</v>
-      </c>
-      <c r="E169">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
@@ -7277,7 +7265,7 @@
         <v>582</v>
       </c>
       <c r="D192" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192" s="2"/>
     </row>
